--- a/docs/downloads/04/tbl_homeland_alaotra_analamiranga.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_analamiranga.xlsx
@@ -397,12 +397,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -419,12 +413,6 @@
         <is>
           <t>2</t>
         </is>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>9.1</v>
       </c>
     </row>
     <row r="4">
